--- a/base_datas/media_uf_detalhamento.xlsx
+++ b/base_datas/media_uf_detalhamento.xlsx
@@ -612,7 +612,7 @@
         <v>4708.919366845685</v>
       </c>
       <c r="E2">
-        <v>148.931963826786</v>
+        <v>148.9319638267861</v>
       </c>
       <c r="F2">
         <v>268.4665554996709</v>
@@ -733,7 +733,7 @@
         <v>7755.219101057429</v>
       </c>
       <c r="E3">
-        <v>504.3930853758276</v>
+        <v>504.3930853758275</v>
       </c>
       <c r="F3">
         <v>361.3245782872646</v>
@@ -851,28 +851,28 @@
         </is>
       </c>
       <c r="B4">
-        <v>262.3330836316928</v>
+        <v>265.7157061210849</v>
       </c>
       <c r="C4">
-        <v>64.06975969110154</v>
+        <v>64.59926098557953</v>
       </c>
       <c r="D4">
-        <v>5801.495897490706</v>
+        <v>5865.991790906533</v>
       </c>
       <c r="E4">
-        <v>93.35467677090958</v>
+        <v>94.67401291819429</v>
       </c>
       <c r="F4">
-        <v>247.3356756352726</v>
+        <v>250.4789798224095</v>
       </c>
       <c r="G4">
-        <v>9.329441654090658</v>
+        <v>9.483414931594757</v>
       </c>
       <c r="H4">
         <v>23.71263988666897</v>
       </c>
       <c r="I4">
-        <v>93.25413918778608</v>
+        <v>95.68784096245298</v>
       </c>
       <c r="J4">
         <v>22.34011478688965</v>
@@ -881,16 +881,16 @@
         <v>7.684498783777746</v>
       </c>
       <c r="L4">
-        <v>3737.022178464857</v>
+        <v>3777.495463260087</v>
       </c>
       <c r="M4">
-        <v>1024.277981300703</v>
+        <v>1035.659803617825</v>
       </c>
       <c r="N4">
-        <v>1040.195737725146</v>
+        <v>1052.836524028621</v>
       </c>
       <c r="O4">
-        <v>70.35762422720502</v>
+        <v>71.29996071933078</v>
       </c>
       <c r="P4">
         <v>22.21340262371529</v>
@@ -899,31 +899,31 @@
         <v>0.001101146161570692</v>
       </c>
       <c r="S4">
-        <v>12.44941111232888</v>
+        <v>12.6569000712176</v>
       </c>
       <c r="T4">
-        <v>7.959743094377467</v>
+        <v>8.102337256135563</v>
       </c>
       <c r="U4">
         <v>4.017368049207844</v>
       </c>
       <c r="V4">
-        <v>108.2189742561933</v>
+        <v>109.6126204241009</v>
       </c>
       <c r="W4">
-        <v>98.51332189038784</v>
+        <v>99.62211648136966</v>
       </c>
       <c r="Z4">
         <v>53.16114547734889</v>
       </c>
       <c r="AA4">
-        <v>6.851357245963422</v>
+        <v>6.973248529501837</v>
       </c>
       <c r="AB4">
-        <v>4.627276059213437</v>
+        <v>4.748839314971013</v>
       </c>
       <c r="AC4">
-        <v>3.423056916593845E-16</v>
+        <v>3.580690879440737E-16</v>
       </c>
       <c r="AE4">
         <v>0.1920357684463735</v>
@@ -935,31 +935,31 @@
         <v>46.61364158392152</v>
       </c>
       <c r="AH4">
-        <v>1440.917720980991</v>
+        <v>1455.954489892467</v>
       </c>
       <c r="AJ4">
-        <v>128.0616838114944</v>
+        <v>127.5382074895752</v>
       </c>
       <c r="AK4">
-        <v>979.3497619924641</v>
+        <v>989.092821510376</v>
       </c>
       <c r="AL4">
-        <v>166.6417162107782</v>
+        <v>168.7673175529735</v>
       </c>
       <c r="AM4">
-        <v>869.6201411579186</v>
+        <v>882.0011315113738</v>
       </c>
       <c r="AN4">
-        <v>59.31429165306485</v>
+        <v>60.15229574806135</v>
       </c>
       <c r="AO4">
-        <v>93.11686265814495</v>
+        <v>93.98919955526034</v>
       </c>
       <c r="AP4">
-        <v>855.044916483629</v>
+        <v>864.7541672539451</v>
       </c>
       <c r="AQ4">
-        <v>16.98220833631826</v>
+        <v>17.24577221628767</v>
       </c>
       <c r="AR4">
         <v>96.97849385210641</v>
@@ -968,10 +968,10 @@
         <v>38.81194067963058</v>
       </c>
       <c r="AT4">
-        <v>7.790905945570604</v>
+        <v>7.8793311287555</v>
       </c>
       <c r="AU4">
-        <v>75.63153317108085</v>
+        <v>75.82378094384552</v>
       </c>
       <c r="AV4">
         <v>1</v>
@@ -1111,22 +1111,22 @@
         </is>
       </c>
       <c r="B6">
-        <v>433.6794197448787</v>
+        <v>434.660197445323</v>
       </c>
       <c r="C6">
-        <v>75.86444452453412</v>
+        <v>76.1730852655908</v>
       </c>
       <c r="D6">
-        <v>5598.413845018443</v>
+        <v>5611.093223484763</v>
       </c>
       <c r="E6">
-        <v>132.5410674461402</v>
+        <v>132.8672018428585</v>
       </c>
       <c r="F6">
-        <v>398.0888919558578</v>
+        <v>398.9842695507434</v>
       </c>
       <c r="G6">
-        <v>34.20047579230813</v>
+        <v>34.28324819968519</v>
       </c>
       <c r="H6">
         <v>21.82446593253701</v>
@@ -1135,22 +1135,22 @@
         <v>201.7613211052404</v>
       </c>
       <c r="J6">
-        <v>51.25410768424558</v>
+        <v>51.4739040520311</v>
       </c>
       <c r="K6">
         <v>0.04072115496403581</v>
       </c>
       <c r="L6">
-        <v>3806.355058723455</v>
+        <v>3815.000647179638</v>
       </c>
       <c r="M6">
-        <v>776.1079829920337</v>
+        <v>777.8332375099791</v>
       </c>
       <c r="N6">
-        <v>1015.950803302954</v>
+        <v>1018.259338795145</v>
       </c>
       <c r="O6">
-        <v>61.96621050364661</v>
+        <v>62.1175968343307</v>
       </c>
       <c r="P6">
         <v>50.98482924496813</v>
@@ -1162,31 +1162,31 @@
         <v>0.2392146017699115</v>
       </c>
       <c r="S6">
-        <v>47.49591997639745</v>
+        <v>47.61377585723218</v>
       </c>
       <c r="T6">
-        <v>34.25032783646806</v>
+        <v>34.32600681413408</v>
       </c>
       <c r="U6">
-        <v>22.31160209988444</v>
+        <v>22.36290611979799</v>
       </c>
       <c r="V6">
-        <v>186.4353351411869</v>
+        <v>186.8317087231802</v>
       </c>
       <c r="W6">
-        <v>155.3179352543457</v>
+        <v>155.7017662415372</v>
       </c>
       <c r="Z6">
-        <v>6.911164432982932</v>
+        <v>6.935245145292978</v>
       </c>
       <c r="AA6">
-        <v>26.51393812760719</v>
+        <v>26.57778461694485</v>
       </c>
       <c r="AB6">
-        <v>11.17015336476996</v>
+        <v>11.21016322131644</v>
       </c>
       <c r="AC6">
-        <v>3.794645696670106E-16</v>
+        <v>3.809273969323537E-16</v>
       </c>
       <c r="AD6">
         <v>13.77368738286023</v>
@@ -1201,43 +1201,43 @@
         <v>0.4359254260015787</v>
       </c>
       <c r="AH6">
-        <v>2020.033599755949</v>
+        <v>2024.573934304344</v>
       </c>
       <c r="AJ6">
-        <v>116.8262065276472</v>
+        <v>117.0492502604045</v>
       </c>
       <c r="AK6">
-        <v>628.1094877084598</v>
+        <v>629.5220467017834</v>
       </c>
       <c r="AL6">
-        <v>151.3757754761841</v>
+        <v>151.7342749794367</v>
       </c>
       <c r="AM6">
-        <v>726.1446511484451</v>
+        <v>727.8692872225452</v>
       </c>
       <c r="AN6">
-        <v>33.80545496532017</v>
+        <v>33.88201801893251</v>
       </c>
       <c r="AO6">
-        <v>135.2930619656342</v>
+        <v>135.6282541516607</v>
       </c>
       <c r="AP6">
-        <v>642.4178882572597</v>
+        <v>643.8772416891256</v>
       </c>
       <c r="AQ6">
-        <v>44.53188941506127</v>
+        <v>44.63403748499388</v>
       </c>
       <c r="AR6">
-        <v>27.39004030159203</v>
+        <v>27.45867243450529</v>
       </c>
       <c r="AS6">
-        <v>11.11107623480018</v>
+        <v>11.13972389721956</v>
       </c>
       <c r="AT6">
         <v>27.91262026169598</v>
       </c>
       <c r="AU6">
-        <v>53.54609717333355</v>
+        <v>53.63544274612898</v>
       </c>
       <c r="AV6">
         <v>1</v>
@@ -1389,7 +1389,7 @@
         <v>2372.308437906705</v>
       </c>
       <c r="E8">
-        <v>1442.628285151825</v>
+        <v>1442.628285151826</v>
       </c>
       <c r="F8">
         <v>8141.057707744824</v>
@@ -1782,7 +1782,7 @@
         <v>5972.807827499785</v>
       </c>
       <c r="E11">
-        <v>106.8817326038466</v>
+        <v>106.8817326038465</v>
       </c>
       <c r="F11">
         <v>253.2302687802361</v>
@@ -1906,22 +1906,22 @@
         </is>
       </c>
       <c r="B12">
-        <v>559.3178158875889</v>
+        <v>560.4886118798178</v>
       </c>
       <c r="C12">
         <v>120.5939137880303</v>
       </c>
       <c r="D12">
-        <v>6690.01703874492</v>
+        <v>6696.209468784184</v>
       </c>
       <c r="E12">
-        <v>326.4285646352271</v>
+        <v>326.8669245454357</v>
       </c>
       <c r="F12">
-        <v>517.4649831836732</v>
+        <v>517.9594461114046</v>
       </c>
       <c r="G12">
-        <v>42.46924306166534</v>
+        <v>42.52960457802858</v>
       </c>
       <c r="H12">
         <v>7.304036979846243</v>
@@ -1936,19 +1936,19 @@
         <v>1.189180556738194</v>
       </c>
       <c r="L12">
-        <v>4163.582784353037</v>
+        <v>4167.668814038783</v>
       </c>
       <c r="M12">
-        <v>1762.618445267366</v>
+        <v>1764.034706003559</v>
       </c>
       <c r="N12">
-        <v>766.8342490939218</v>
+        <v>767.5305189030198</v>
       </c>
       <c r="O12">
-        <v>207.5648552398792</v>
+        <v>207.9923409791859</v>
       </c>
       <c r="P12">
-        <v>65.7823963747566</v>
+        <v>65.62748201613198</v>
       </c>
       <c r="Q12">
         <v>2.383841222322468</v>
@@ -1957,28 +1957,28 @@
         <v>8.969974893518955</v>
       </c>
       <c r="S12">
-        <v>73.46623803931823</v>
+        <v>73.63168910767622</v>
       </c>
       <c r="T12">
-        <v>68.21941192410914</v>
+        <v>68.28907346756571</v>
       </c>
       <c r="U12">
-        <v>59.12005355870424</v>
+        <v>59.16505029684699</v>
       </c>
       <c r="V12">
-        <v>245.2793268740402</v>
+        <v>245.5293450831224</v>
       </c>
       <c r="W12">
-        <v>144.9641008433606</v>
+        <v>145.0947915812571</v>
       </c>
       <c r="Z12">
-        <v>0.9371757304941631</v>
+        <v>0.9386728163256235</v>
       </c>
       <c r="AA12">
         <v>18.51226325928285</v>
       </c>
       <c r="AB12">
-        <v>26.82571802736989</v>
+        <v>26.84943649792857</v>
       </c>
       <c r="AC12">
         <v>-8.319584872903121E-17</v>
@@ -1996,43 +1996,43 @@
         <v>5.866912234611815</v>
       </c>
       <c r="AH12">
-        <v>3130.805540316365</v>
+        <v>3133.857907943199</v>
       </c>
       <c r="AJ12">
-        <v>249.6313297438916</v>
+        <v>249.9150082497604</v>
       </c>
       <c r="AK12">
-        <v>576.6275563156247</v>
+        <v>577.1712109594948</v>
       </c>
       <c r="AL12">
-        <v>79.84835759858646</v>
+        <v>79.91892167357794</v>
       </c>
       <c r="AM12">
         <v>51.5591667477426</v>
       </c>
       <c r="AN12">
-        <v>32.80314358447182</v>
+        <v>32.83444050352398</v>
       </c>
       <c r="AO12">
-        <v>74.67090672407186</v>
+        <v>74.75324902688054</v>
       </c>
       <c r="AP12">
-        <v>1199.994435847319</v>
+        <v>1201.071782299965</v>
       </c>
       <c r="AQ12">
-        <v>178.1785496160331</v>
+        <v>178.3408414126766</v>
       </c>
       <c r="AR12">
-        <v>233.2494939038591</v>
+        <v>233.4412168393657</v>
       </c>
       <c r="AS12">
-        <v>12.96720980003402</v>
+        <v>12.98139557277382</v>
       </c>
       <c r="AT12">
-        <v>26.24968432468973</v>
+        <v>25.10681004231635</v>
       </c>
       <c r="AU12">
-        <v>135.8162136283985</v>
+        <v>135.9668375617031</v>
       </c>
       <c r="AV12">
         <v>1</v>
@@ -2054,7 +2054,7 @@
         <v>7879.125359733186</v>
       </c>
       <c r="E13">
-        <v>396.3526406934384</v>
+        <v>396.3526406934383</v>
       </c>
       <c r="F13">
         <v>1259.759835951065</v>
@@ -2190,7 +2190,7 @@
         <v>8470.13650957145</v>
       </c>
       <c r="E14">
-        <v>478.0235391171644</v>
+        <v>478.0235391171645</v>
       </c>
       <c r="F14">
         <v>1129.848826635405</v>
@@ -2326,7 +2326,7 @@
         <v>5337.190238863629</v>
       </c>
       <c r="E15">
-        <v>93.71588198977786</v>
+        <v>93.71588198977788</v>
       </c>
       <c r="F15">
         <v>421.429748116895</v>
@@ -2586,7 +2586,7 @@
         <v>4999.372284330724</v>
       </c>
       <c r="E17">
-        <v>170.6006763717683</v>
+        <v>170.6006763717682</v>
       </c>
       <c r="F17">
         <v>285.2004929766968</v>
@@ -2834,49 +2834,49 @@
         </is>
       </c>
       <c r="B19">
-        <v>813.0150276083922</v>
+        <v>813.2887080217901</v>
       </c>
       <c r="C19">
-        <v>271.7774555486627</v>
+        <v>241.3272856067826</v>
       </c>
       <c r="D19">
-        <v>6807.455885105423</v>
+        <v>6814.786188787054</v>
       </c>
       <c r="E19">
-        <v>662.3468139723891</v>
+        <v>558.101685595336</v>
       </c>
       <c r="F19">
-        <v>730.8300199419215</v>
+        <v>731.0409269844856</v>
       </c>
       <c r="G19">
-        <v>79.70474650773673</v>
+        <v>79.83252405007397</v>
       </c>
       <c r="H19">
-        <v>8.329260790259578</v>
+        <v>8.15493993666176</v>
       </c>
       <c r="I19">
         <v>328.8865309312581</v>
       </c>
       <c r="J19">
-        <v>96.77840864523954</v>
+        <v>97.02355574500037</v>
       </c>
       <c r="K19">
-        <v>103.0294294433259</v>
+        <v>2.278076421975716</v>
       </c>
       <c r="L19">
-        <v>3882.927763480561</v>
+        <v>3882.074891139171</v>
       </c>
       <c r="M19">
-        <v>2072.602750931359</v>
+        <v>2082.270395313806</v>
       </c>
       <c r="N19">
-        <v>851.9253706935024</v>
+        <v>850.4409023340771</v>
       </c>
       <c r="O19">
-        <v>457.5377734304228</v>
+        <v>376.8535440503898</v>
       </c>
       <c r="P19">
-        <v>102.2789697252265</v>
+        <v>75.51139578358242</v>
       </c>
       <c r="Q19">
         <v>7.343668814182406</v>
@@ -2885,28 +2885,28 @@
         <v>1.787890257588648</v>
       </c>
       <c r="S19">
-        <v>115.5025753907528</v>
+        <v>115.1289510814973</v>
       </c>
       <c r="T19">
-        <v>153.6750004779365</v>
+        <v>153.96796757717</v>
       </c>
       <c r="U19">
-        <v>113.2296048287508</v>
+        <v>113.2641421414813</v>
       </c>
       <c r="V19">
-        <v>229.6604294240862</v>
+        <v>229.9081931725803</v>
       </c>
       <c r="W19">
-        <v>234.0852177512019</v>
+        <v>233.7229675209146</v>
       </c>
       <c r="Z19">
-        <v>3.299610877021422</v>
+        <v>3.32191214523297</v>
       </c>
       <c r="AA19">
-        <v>26.00918176457087</v>
+        <v>26.02312459116534</v>
       </c>
       <c r="AB19">
-        <v>55.58772242680706</v>
+        <v>55.71483825977435</v>
       </c>
       <c r="AC19">
         <v>1.650411277446647E-15</v>
@@ -2918,46 +2918,46 @@
         <v>16.14533148194797</v>
       </c>
       <c r="AG19">
-        <v>31.41467137307395</v>
+        <v>31.49562786576691</v>
       </c>
       <c r="AH19">
-        <v>3014.025153787346</v>
+        <v>3028.208136340425</v>
       </c>
       <c r="AJ19">
-        <v>107.6389615501287</v>
+        <v>106.1119062287885</v>
       </c>
       <c r="AK19">
-        <v>400.3344514261554</v>
+        <v>401.9688448911879</v>
       </c>
       <c r="AL19">
-        <v>90.57445806365219</v>
+        <v>91.00817461700383</v>
       </c>
       <c r="AM19">
-        <v>26.50526099123362</v>
+        <v>26.61808517566456</v>
       </c>
       <c r="AN19">
-        <v>29.47019822365968</v>
+        <v>29.47291456650678</v>
       </c>
       <c r="AO19">
-        <v>243.5970900392391</v>
+        <v>227.821419812025</v>
       </c>
       <c r="AP19">
-        <v>1668.112289822819</v>
+        <v>1671.876886577271</v>
       </c>
       <c r="AQ19">
-        <v>212.8809355824115</v>
+        <v>213.41301742201</v>
       </c>
       <c r="AR19">
-        <v>74.06581423971836</v>
+        <v>74.22501626246714</v>
       </c>
       <c r="AS19">
         <v>21.00716058975033</v>
       </c>
       <c r="AT19">
-        <v>8.62550350173383</v>
+        <v>8.523758241258573</v>
       </c>
       <c r="AU19">
-        <v>116.0188986711899</v>
+        <v>116.3278386646423</v>
       </c>
       <c r="AV19">
         <v>1</v>
@@ -2979,7 +2979,7 @@
         <v>7366.452549905876</v>
       </c>
       <c r="E20">
-        <v>583.6781852223017</v>
+        <v>583.678185222302</v>
       </c>
       <c r="F20">
         <v>1080.172970975859</v>
@@ -3112,7 +3112,7 @@
         <v>6861.477492561828</v>
       </c>
       <c r="E21">
-        <v>157.6782216178646</v>
+        <v>158.6575894540004</v>
       </c>
       <c r="F21">
         <v>421.6398123060395</v>
@@ -3230,46 +3230,46 @@
         </is>
       </c>
       <c r="B22">
-        <v>654.4236350071167</v>
+        <v>660.4484803814677</v>
       </c>
       <c r="C22">
-        <v>170.6628518797059</v>
+        <v>169.7763829580181</v>
       </c>
       <c r="D22">
-        <v>6199.746019279012</v>
+        <v>6307.256894321244</v>
       </c>
       <c r="E22">
-        <v>474.7278068444827</v>
+        <v>475.3426204914207</v>
       </c>
       <c r="F22">
-        <v>565.4024571130765</v>
+        <v>570.1685107648406</v>
       </c>
       <c r="G22">
-        <v>87.35177222786412</v>
+        <v>88.57783050601614</v>
       </c>
       <c r="H22">
         <v>21.70227366028887</v>
       </c>
       <c r="I22">
-        <v>199.8487311536709</v>
+        <v>200.7054354817909</v>
       </c>
       <c r="J22">
-        <v>55.79300854136184</v>
+        <v>56.20280094996082</v>
       </c>
       <c r="K22">
-        <v>0.02283210273457037</v>
+        <v>0.0242591091554805</v>
       </c>
       <c r="L22">
-        <v>2753.912867486845</v>
+        <v>2795.782404870768</v>
       </c>
       <c r="M22">
-        <v>2448.113551904918</v>
+        <v>2494.273100431221</v>
       </c>
       <c r="N22">
-        <v>997.7195998872493</v>
+        <v>1017.201389019255</v>
       </c>
       <c r="O22">
-        <v>372.6121021613991</v>
+        <v>372.1077218446509</v>
       </c>
       <c r="P22">
         <v>53.47757141276175</v>
@@ -3278,28 +3278,28 @@
         <v>0.02751221529950105</v>
       </c>
       <c r="S22">
-        <v>64.06382671217044</v>
+        <v>64.43690542152491</v>
       </c>
       <c r="T22">
-        <v>83.19793666343828</v>
+        <v>84.09650341319976</v>
       </c>
       <c r="U22">
-        <v>73.573535990463</v>
+        <v>74.3324437020264</v>
       </c>
       <c r="V22">
-        <v>192.6918256654515</v>
+        <v>194.3217959565434</v>
       </c>
       <c r="W22">
-        <v>215.8762462990608</v>
+        <v>217.3536216200814</v>
       </c>
       <c r="Z22">
-        <v>0.08178624306182554</v>
+        <v>0.08388332621725528</v>
       </c>
       <c r="AA22">
-        <v>31.57054394820379</v>
+        <v>32.0617949461753</v>
       </c>
       <c r="AB22">
-        <v>58.01247741084675</v>
+        <v>58.82281252146699</v>
       </c>
       <c r="AC22">
         <v>-4.163700954427681E-15</v>
@@ -3311,16 +3311,16 @@
         <v>28.11545457766758</v>
       </c>
       <c r="AH22">
-        <v>1822.490368291183</v>
+        <v>1852.376465022217</v>
       </c>
       <c r="AJ22">
-        <v>60.18740174195143</v>
+        <v>60.74874112500805</v>
       </c>
       <c r="AK22">
-        <v>617.8939406409702</v>
+        <v>626.4267843235408</v>
       </c>
       <c r="AL22">
-        <v>87.10740325954656</v>
+        <v>87.17071564276652</v>
       </c>
       <c r="AM22">
         <v>18.12880586005885</v>
@@ -3329,7 +3329,7 @@
         <v>29.35983297235399</v>
       </c>
       <c r="AO22">
-        <v>128.4574615226735</v>
+        <v>130.5426951182728</v>
       </c>
       <c r="AP22">
         <v>1925.581304027521</v>
@@ -3347,7 +3347,7 @@
         <v>9.710327707637118</v>
       </c>
       <c r="AU22">
-        <v>354.0513284849845</v>
+        <v>359.1508334148186</v>
       </c>
       <c r="AV22">
         <v>1</v>
@@ -3369,7 +3369,7 @@
         <v>4920.527279381608</v>
       </c>
       <c r="E23">
-        <v>153.0179512794123</v>
+        <v>153.0179512794122</v>
       </c>
       <c r="F23">
         <v>413.3163482393508</v>
@@ -3629,7 +3629,7 @@
         <v>7483.124362966222</v>
       </c>
       <c r="E25">
-        <v>479.2849286659094</v>
+        <v>479.2849286659095</v>
       </c>
       <c r="F25">
         <v>910.7236983759599</v>
@@ -4022,7 +4022,7 @@
         <v>8947.297161174647</v>
       </c>
       <c r="E28">
-        <v>451.3162177596303</v>
+        <v>451.3162177596305</v>
       </c>
       <c r="F28">
         <v>-535.6041903169684</v>
